--- a/doc/templates/Hango_Exam_Import_Template.xlsx
+++ b/doc/templates/Hango_Exam_Import_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Summer2026\SEP490\project\HanGo\doc\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFE8D0F-1B02-451C-A992-48618C837AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709105CE-D2B7-423C-AA89-485C0C458CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README_AND_RULES" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
   <si>
     <t>2. Sheets to fill in:</t>
   </si>
@@ -36,9 +36,6 @@
     <t>4. After filling in the information, upload this file to the system.</t>
   </si>
   <si>
-    <t xml:space="preserve">   The system will automatically generate the entire course structure.</t>
-  </si>
-  <si>
     <t>Title</t>
   </si>
   <si>
@@ -51,12 +48,6 @@
     <t>Thumbnail URL</t>
   </si>
   <si>
-    <t>Simple Present</t>
-  </si>
-  <si>
-    <t>Simple Past</t>
-  </si>
-  <si>
     <t>Order Index</t>
   </si>
   <si>
@@ -99,12 +90,6 @@
     <t>EXAM OVERVIEW</t>
   </si>
   <si>
-    <t>EXAM_001</t>
-  </si>
-  <si>
-    <t>EXAM_002</t>
-  </si>
-  <si>
     <t xml:space="preserve">   - Exam: Main exam information</t>
   </si>
   <si>
@@ -123,12 +108,6 @@
     <t>Passing Score</t>
   </si>
   <si>
-    <t>This exam provides all knowledges about simple present tense</t>
-  </si>
-  <si>
-    <t>This exam provides all knowledges about simple past tense</t>
-  </si>
-  <si>
     <t xml:space="preserve">   - Question Count must be greater than 2 and less than or equal to 100</t>
   </si>
   <si>
@@ -249,25 +228,7 @@
     <t xml:space="preserve">   - Passage Text(optional): contains the content of the paragraph in the multiple question</t>
   </si>
   <si>
-    <t>tttt</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>abc</t>
-  </si>
-  <si>
-    <t>phonetics</t>
-  </si>
-  <si>
-    <t>easy</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>medium</t>
+    <t xml:space="preserve">   The system will automatically generate the entire exam structure.</t>
   </si>
 </sst>
 </file>
@@ -503,25 +464,25 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -841,7 +802,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" ht="22.8">
       <c r="A1" s="8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="22.8">
@@ -849,7 +810,7 @@
     </row>
     <row r="3" spans="1:3" ht="15.6">
       <c r="A3" s="10" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B3" s="11"/>
     </row>
@@ -865,13 +826,13 @@
     </row>
     <row r="6" spans="1:3" ht="15">
       <c r="A6" s="18" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B6" s="11"/>
     </row>
     <row r="7" spans="1:3" ht="15">
       <c r="A7" s="18" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B7" s="11"/>
     </row>
@@ -893,242 +854,242 @@
     </row>
     <row r="11" spans="1:3" customFormat="1">
       <c r="A11" s="19" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B11" s="14"/>
     </row>
     <row r="12" spans="1:3" customFormat="1">
       <c r="A12" s="19" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B12" s="14"/>
     </row>
     <row r="13" spans="1:3" customFormat="1">
       <c r="A13" s="19" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B13" s="14"/>
     </row>
     <row r="14" spans="1:3" customFormat="1" ht="14.4" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="14"/>
     </row>
     <row r="15" spans="1:3" customFormat="1">
       <c r="A15" s="19" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B15" s="14"/>
     </row>
     <row r="16" spans="1:3" customFormat="1">
       <c r="A16" s="19" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B16" s="14"/>
     </row>
     <row r="17" spans="1:2" customFormat="1">
       <c r="A17" s="19" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B17" s="14"/>
     </row>
     <row r="18" spans="1:2" customFormat="1">
       <c r="A18" s="19" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B18" s="14"/>
     </row>
     <row r="19" spans="1:2" customFormat="1">
       <c r="A19" s="19" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B19" s="14"/>
     </row>
     <row r="20" spans="1:2" customFormat="1">
       <c r="A20" s="19" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B20" s="14"/>
     </row>
     <row r="21" spans="1:2" customFormat="1">
       <c r="A21" s="19" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B21" s="14"/>
     </row>
     <row r="22" spans="1:2" customFormat="1">
       <c r="A22" s="19" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B22" s="14"/>
     </row>
     <row r="23" spans="1:2" customFormat="1">
       <c r="A23" s="19" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B23" s="14"/>
     </row>
     <row r="24" spans="1:2" customFormat="1">
       <c r="A24" s="19" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B24" s="14"/>
     </row>
     <row r="25" spans="1:2" customFormat="1">
       <c r="A25" s="19" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B25" s="14"/>
     </row>
     <row r="26" spans="1:2" customFormat="1">
       <c r="A26" s="19" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B26" s="14"/>
     </row>
     <row r="27" spans="1:2" customFormat="1">
       <c r="A27" s="19" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B27" s="14"/>
     </row>
     <row r="28" spans="1:2" customFormat="1">
       <c r="A28" s="19" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B28" s="14"/>
     </row>
     <row r="29" spans="1:2" customFormat="1">
       <c r="A29" s="19" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B29" s="14"/>
     </row>
     <row r="30" spans="1:2" customFormat="1">
       <c r="A30" s="19" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B30" s="14"/>
     </row>
     <row r="31" spans="1:2" customFormat="1">
       <c r="A31" s="19" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B31" s="14"/>
     </row>
     <row r="32" spans="1:2" customFormat="1">
       <c r="A32" s="19" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B32" s="14"/>
     </row>
     <row r="33" spans="1:2" customFormat="1">
       <c r="A33" s="19" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B33" s="14"/>
     </row>
     <row r="34" spans="1:2" customFormat="1">
       <c r="A34" s="19" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B34" s="14"/>
     </row>
     <row r="35" spans="1:2" customFormat="1">
       <c r="A35" s="19" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B35" s="14"/>
     </row>
     <row r="36" spans="1:2" customFormat="1">
       <c r="A36" s="19" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B36" s="14"/>
     </row>
     <row r="37" spans="1:2" customFormat="1">
       <c r="A37" s="19" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B37" s="14"/>
     </row>
     <row r="38" spans="1:2" customFormat="1">
       <c r="A38" s="19" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B38" s="14"/>
     </row>
     <row r="39" spans="1:2" customFormat="1">
       <c r="A39" s="19" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B39" s="14"/>
     </row>
     <row r="40" spans="1:2" customFormat="1">
       <c r="A40" s="19" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B40" s="14"/>
     </row>
     <row r="41" spans="1:2" customFormat="1">
       <c r="A41" s="19" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B41" s="14"/>
     </row>
     <row r="42" spans="1:2" customFormat="1">
       <c r="A42" s="19" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B42" s="14"/>
     </row>
     <row r="43" spans="1:2" customFormat="1">
       <c r="A43" s="19" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B43" s="14"/>
     </row>
     <row r="44" spans="1:2" customFormat="1">
       <c r="A44" s="19" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B44" s="14"/>
     </row>
     <row r="45" spans="1:2" customFormat="1">
       <c r="A45" s="19" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B45" s="14"/>
     </row>
     <row r="46" spans="1:2" customFormat="1">
       <c r="A46" s="19" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B46" s="14"/>
     </row>
     <row r="47" spans="1:2" customFormat="1">
       <c r="A47" s="19" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B47" s="14"/>
     </row>
     <row r="48" spans="1:2" customFormat="1">
       <c r="A48" s="19" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B48" s="14"/>
     </row>
     <row r="49" spans="1:2" customFormat="1">
       <c r="A49" s="19" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B49" s="14"/>
     </row>
     <row r="50" spans="1:2" customFormat="1">
       <c r="A50" s="19" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B50" s="14"/>
     </row>
@@ -1140,7 +1101,7 @@
     </row>
     <row r="52" spans="1:2" customFormat="1">
       <c r="A52" s="13" t="s">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="B52" s="14"/>
     </row>
@@ -1206,227 +1167,198 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.8">
-      <c r="A1" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="A1" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" s="6"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="23">
-        <v>20</v>
-      </c>
-      <c r="E3" s="23">
-        <v>7</v>
-      </c>
-      <c r="F3" s="23"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="23">
-        <v>10</v>
-      </c>
-      <c r="E8" s="23">
-        <v>7</v>
-      </c>
-      <c r="F8" s="23"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="24"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="22"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="25"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="23"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="23"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="25"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="23"/>
     </row>
     <row r="16" spans="1:7" ht="12" customHeight="1">
-      <c r="A16" s="23"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="25"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="23"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="26"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="24"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="24"/>
+      <c r="A18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="22"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="25"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="23"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="23"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="25"/>
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="23"/>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="23"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="25"/>
+      <c r="A21" s="25"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="23"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="26"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="F18:F22"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="D8:D12"/>
-    <mergeCell ref="D13:D17"/>
-    <mergeCell ref="D18:D22"/>
-    <mergeCell ref="E3:E7"/>
-    <mergeCell ref="E8:E12"/>
-    <mergeCell ref="E13:E17"/>
-    <mergeCell ref="E18:E22"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A8:A12"/>
@@ -1443,6 +1375,15 @@
     <mergeCell ref="F3:F7"/>
     <mergeCell ref="F8:F12"/>
     <mergeCell ref="F13:F17"/>
+    <mergeCell ref="F18:F22"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="D8:D12"/>
+    <mergeCell ref="D13:D17"/>
+    <mergeCell ref="D18:D22"/>
+    <mergeCell ref="E3:E7"/>
+    <mergeCell ref="E8:E12"/>
+    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="E18:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1465,134 +1406,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="22.8">
-      <c r="C1" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
+      <c r="C1" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
     </row>
     <row r="2" spans="1:13" s="2" customFormat="1" ht="30" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="E2" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="G2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="H2" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="I2" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="J2" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="K2" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>21</v>
-      </c>
       <c r="L2" s="20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M2" s="20" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="19.95" customHeight="1">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K3" t="s">
-        <v>78</v>
-      </c>
-      <c r="L3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="19.95" customHeight="1">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>4</v>
-      </c>
-      <c r="I4" t="s">
-        <v>80</v>
-      </c>
-      <c r="J4" t="s">
-        <v>77</v>
-      </c>
-      <c r="K4" t="s">
-        <v>78</v>
-      </c>
-      <c r="L4" t="s">
-        <v>81</v>
-      </c>
-    </row>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="19.95" customHeight="1"/>
+    <row r="4" spans="1:13" ht="19.95" customHeight="1"/>
     <row r="5" spans="1:13" ht="19.95" customHeight="1"/>
     <row r="6" spans="1:13" ht="19.95" customHeight="1"/>
     <row r="7" spans="1:13" ht="19.95" customHeight="1"/>

--- a/doc/templates/Hango_Exam_Import_Template.xlsx
+++ b/doc/templates/Hango_Exam_Import_Template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9707" activeTab="1"/>
+    <workbookView windowWidth="23028" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="README_AND_RULES" sheetId="1" r:id="rId1"/>

--- a/doc/templates/Hango_Exam_Import_Template.xlsx
+++ b/doc/templates/Hango_Exam_Import_Template.xlsx
@@ -1,28 +1,71 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Summer2026\SEP490\project\HanGo\doc\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE039501-A3F6-42C9-9A47-D8BBB26554F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25D54CD-12B9-4611-A6E4-6E5BB2F85BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README_AND_RULES" sheetId="1" r:id="rId1"/>
     <sheet name="EXAM" sheetId="2" r:id="rId2"/>
-    <sheet name="QUESTIONS" sheetId="6" r:id="rId3"/>
+    <sheet name="QUESTIONS" sheetId="3" r:id="rId3"/>
+    <sheet name="LISTS_DATA" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="107">
+  <si>
+    <t>QUESTIONS</t>
+  </si>
+  <si>
+    <t>Exam Code</t>
+  </si>
+  <si>
+    <t>Order Index</t>
+  </si>
+  <si>
+    <t>Passage Text</t>
+  </si>
+  <si>
+    <t>Question Text</t>
+  </si>
+  <si>
+    <t>Option A</t>
+  </si>
+  <si>
+    <t>Option B</t>
+  </si>
+  <si>
+    <t>Option C</t>
+  </si>
+  <si>
+    <t>Option D</t>
+  </si>
+  <si>
+    <t>Correct Answer</t>
+  </si>
+  <si>
+    <t>Explaination</t>
+  </si>
+  <si>
+    <t>Skill Type</t>
+  </si>
+  <si>
+    <t>Difficulty</t>
+  </si>
+  <si>
+    <t>Group Type</t>
+  </si>
   <si>
     <t>Hango Exam Import Template - Rules</t>
   </si>
@@ -174,9 +217,6 @@
     <t>EXAM OVERVIEW</t>
   </si>
   <si>
-    <t>Exam Code</t>
-  </si>
-  <si>
     <t>Title</t>
   </si>
   <si>
@@ -195,50 +235,122 @@
     <t>Thumbnail URL</t>
   </si>
   <si>
-    <t>QUESTIONS</t>
-  </si>
-  <si>
-    <t>Order Index</t>
-  </si>
-  <si>
-    <t>Passage Text</t>
-  </si>
-  <si>
-    <t>Question Text</t>
-  </si>
-  <si>
-    <t>Option A</t>
-  </si>
-  <si>
-    <t>Option B</t>
-  </si>
-  <si>
-    <t>Option C</t>
-  </si>
-  <si>
-    <t>Option D</t>
-  </si>
-  <si>
-    <t>Correct Answer</t>
-  </si>
-  <si>
-    <t>Explaination</t>
-  </si>
-  <si>
-    <t>Skill Type</t>
-  </si>
-  <si>
-    <t>Difficulty</t>
-  </si>
-  <si>
-    <t>Group Type</t>
+    <t>Phonetics</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>Read and Fill in a Notice</t>
+  </si>
+  <si>
+    <t>Word order</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Read and Fill in a Leaflet/Advertisement</t>
+  </si>
+  <si>
+    <t>Reduced relative clause</t>
+  </si>
+  <si>
+    <t>Hard</t>
+  </si>
+  <si>
+    <t>Paragraph/Text Reordering</t>
+  </si>
+  <si>
+    <t>Preposition</t>
+  </si>
+  <si>
+    <t>Very Hard</t>
+  </si>
+  <si>
+    <t>Guided Cloze Test</t>
+  </si>
+  <si>
+    <t>Collocation</t>
+  </si>
+  <si>
+    <t>Reading Comprehension - 8 questions</t>
+  </si>
+  <si>
+    <t>To-infinitive</t>
+  </si>
+  <si>
+    <t>Reading Comprehension - 10 questions</t>
+  </si>
+  <si>
+    <t>Quantifier</t>
+  </si>
+  <si>
+    <t>Phrasal verb</t>
+  </si>
+  <si>
+    <t>Prepositional phrase</t>
+  </si>
+  <si>
+    <t>Vocabulary</t>
+  </si>
+  <si>
+    <t>Conversation ordering</t>
+  </si>
+  <si>
+    <t>Letter ordering</t>
+  </si>
+  <si>
+    <t>Paragraph ordering</t>
+  </si>
+  <si>
+    <t>Passive voice</t>
+  </si>
+  <si>
+    <t>Relative clause</t>
+  </si>
+  <si>
+    <t>Contextual meaning</t>
+  </si>
+  <si>
+    <t>Factual / Detail question</t>
+  </si>
+  <si>
+    <t>Synonym in context</t>
+  </si>
+  <si>
+    <t>Antonym in context</t>
+  </si>
+  <si>
+    <t>Reference question</t>
+  </si>
+  <si>
+    <t>Paraphrasing question</t>
+  </si>
+  <si>
+    <t>Paragraph-specific information question</t>
+  </si>
+  <si>
+    <t>Main idea / Central theme question</t>
+  </si>
+  <si>
+    <t>TRUE / NOT TRUE question</t>
+  </si>
+  <si>
+    <t>Inference question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      + Sentence insertion</t>
+  </si>
+  <si>
+    <t>Sentence insertion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,12 +383,6 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -350,7 +456,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -397,11 +503,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -418,43 +548,43 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -464,11 +594,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFCCFFCC"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -765,321 +890,324 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="114" style="8" customWidth="1"/>
     <col min="2" max="2" width="68.296875" style="8" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="8"/>
+    <col min="3" max="3" width="9" style="8" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="7" customFormat="1" ht="22.8">
+    <row r="1" spans="1:3" s="7" customFormat="1" ht="22.8" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="22.8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="22.8" customHeight="1">
       <c r="A2" s="10"/>
     </row>
-    <row r="3" spans="1:3" ht="15.6">
+    <row r="3" spans="1:3" ht="15.6" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B3" s="12"/>
     </row>
-    <row r="4" spans="1:3" ht="15">
+    <row r="4" spans="1:3" ht="15" customHeight="1">
       <c r="A4" s="13"/>
       <c r="B4" s="12"/>
     </row>
-    <row r="5" spans="1:3" ht="15.6">
+    <row r="5" spans="1:3" ht="15.6" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B5" s="12"/>
     </row>
-    <row r="6" spans="1:3" ht="15">
+    <row r="6" spans="1:3" ht="15" customHeight="1">
       <c r="A6" s="19" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B6" s="12"/>
     </row>
-    <row r="7" spans="1:3" ht="15">
+    <row r="7" spans="1:3" ht="15" customHeight="1">
       <c r="A7" s="19" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B7" s="12"/>
     </row>
-    <row r="8" spans="1:3" ht="15">
+    <row r="8" spans="1:3" ht="15" customHeight="1">
       <c r="A8" s="13"/>
       <c r="B8" s="12"/>
     </row>
-    <row r="9" spans="1:3" ht="15.6">
+    <row r="9" spans="1:3" ht="15.6" customHeight="1">
       <c r="A9" s="11" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B9" s="12"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="20" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B10" s="12"/>
     </row>
-    <row r="11" spans="1:3" customFormat="1">
+    <row r="11" spans="1:3">
       <c r="A11" s="20" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B11" s="15"/>
     </row>
-    <row r="12" spans="1:3" customFormat="1">
+    <row r="12" spans="1:3">
       <c r="A12" s="20" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B12" s="15"/>
     </row>
-    <row r="13" spans="1:3" customFormat="1">
+    <row r="13" spans="1:3">
       <c r="A13" s="20" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B13" s="15"/>
     </row>
-    <row r="14" spans="1:3" customFormat="1" ht="14.4" customHeight="1">
+    <row r="14" spans="1:3" ht="14.4" customHeight="1">
       <c r="A14" s="8" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="15"/>
     </row>
-    <row r="15" spans="1:3" customFormat="1">
+    <row r="15" spans="1:3">
       <c r="A15" s="20" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B15" s="15"/>
     </row>
-    <row r="16" spans="1:3" customFormat="1">
+    <row r="16" spans="1:3">
       <c r="A16" s="20" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B16" s="15"/>
     </row>
-    <row r="17" spans="1:2" customFormat="1">
+    <row r="17" spans="1:2">
       <c r="A17" s="20" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B17" s="15"/>
     </row>
-    <row r="18" spans="1:2" customFormat="1">
+    <row r="18" spans="1:2">
       <c r="A18" s="20" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B18" s="15"/>
     </row>
-    <row r="19" spans="1:2" customFormat="1">
+    <row r="19" spans="1:2">
       <c r="A19" s="20" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B19" s="15"/>
     </row>
-    <row r="20" spans="1:2" customFormat="1">
+    <row r="20" spans="1:2">
       <c r="A20" s="20" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B20" s="15"/>
     </row>
-    <row r="21" spans="1:2" customFormat="1">
+    <row r="21" spans="1:2">
       <c r="A21" s="20" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B21" s="15"/>
     </row>
-    <row r="22" spans="1:2" customFormat="1">
+    <row r="22" spans="1:2">
       <c r="A22" s="20" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B22" s="15"/>
     </row>
-    <row r="23" spans="1:2" customFormat="1">
+    <row r="23" spans="1:2">
       <c r="A23" s="20" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B23" s="15"/>
     </row>
-    <row r="24" spans="1:2" customFormat="1">
+    <row r="24" spans="1:2">
       <c r="A24" s="20" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B24" s="15"/>
     </row>
-    <row r="25" spans="1:2" customFormat="1">
+    <row r="25" spans="1:2">
       <c r="A25" s="20" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B25" s="15"/>
     </row>
-    <row r="26" spans="1:2" customFormat="1">
+    <row r="26" spans="1:2">
       <c r="A26" s="20" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B26" s="15"/>
     </row>
-    <row r="27" spans="1:2" customFormat="1">
+    <row r="27" spans="1:2">
       <c r="A27" s="20" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="B27" s="15"/>
     </row>
-    <row r="28" spans="1:2" customFormat="1">
+    <row r="28" spans="1:2">
       <c r="A28" s="20" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B28" s="15"/>
     </row>
-    <row r="29" spans="1:2" customFormat="1">
+    <row r="29" spans="1:2">
       <c r="A29" s="20" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B29" s="15"/>
     </row>
-    <row r="30" spans="1:2" customFormat="1">
+    <row r="30" spans="1:2">
       <c r="A30" s="20" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B30" s="15"/>
     </row>
-    <row r="31" spans="1:2" customFormat="1">
+    <row r="31" spans="1:2">
       <c r="A31" s="20" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B31" s="15"/>
     </row>
-    <row r="32" spans="1:2" customFormat="1">
+    <row r="32" spans="1:2">
       <c r="A32" s="20" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B32" s="15"/>
     </row>
-    <row r="33" spans="1:2" customFormat="1">
+    <row r="33" spans="1:2">
       <c r="A33" s="20" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B33" s="15"/>
     </row>
-    <row r="34" spans="1:2" customFormat="1">
+    <row r="34" spans="1:2">
       <c r="A34" s="20" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B34" s="15"/>
     </row>
-    <row r="35" spans="1:2" customFormat="1">
+    <row r="35" spans="1:2">
       <c r="A35" s="20" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B35" s="15"/>
     </row>
-    <row r="36" spans="1:2" customFormat="1">
+    <row r="36" spans="1:2">
       <c r="A36" s="20" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B36" s="15"/>
     </row>
-    <row r="37" spans="1:2" customFormat="1">
+    <row r="37" spans="1:2">
       <c r="A37" s="20" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B37" s="15"/>
     </row>
-    <row r="38" spans="1:2" customFormat="1">
+    <row r="38" spans="1:2">
       <c r="A38" s="20" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="B38" s="15"/>
     </row>
-    <row r="39" spans="1:2" customFormat="1">
+    <row r="39" spans="1:2">
       <c r="A39" s="20" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B39" s="15"/>
     </row>
-    <row r="40" spans="1:2" customFormat="1">
+    <row r="40" spans="1:2">
       <c r="A40" s="20" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B40" s="15"/>
     </row>
-    <row r="41" spans="1:2" customFormat="1">
+    <row r="41" spans="1:2">
       <c r="A41" s="20" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B41" s="15"/>
     </row>
-    <row r="42" spans="1:2" customFormat="1">
+    <row r="42" spans="1:2">
       <c r="A42" s="20" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="B42" s="15"/>
     </row>
-    <row r="43" spans="1:2" customFormat="1">
+    <row r="43" spans="1:2">
       <c r="A43" s="20" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B43" s="15"/>
     </row>
-    <row r="44" spans="1:2" customFormat="1">
+    <row r="44" spans="1:2">
       <c r="A44" s="20" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B44" s="15"/>
     </row>
-    <row r="45" spans="1:2" customFormat="1">
+    <row r="45" spans="1:2">
       <c r="A45" s="20" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B45" s="15"/>
     </row>
-    <row r="46" spans="1:2" customFormat="1">
+    <row r="46" spans="1:2">
       <c r="A46" s="20" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B46" s="15"/>
     </row>
-    <row r="47" spans="1:2" customFormat="1">
+    <row r="47" spans="1:2">
       <c r="A47" s="20" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B47" s="15"/>
     </row>
-    <row r="48" spans="1:2" customFormat="1">
+    <row r="48" spans="1:2">
       <c r="A48" s="20" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B48" s="15"/>
     </row>
-    <row r="49" spans="1:2" customFormat="1">
+    <row r="49" spans="1:2">
       <c r="A49" s="20" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B49" s="15"/>
     </row>
-    <row r="50" spans="1:2" customFormat="1">
+    <row r="50" spans="1:2">
       <c r="A50" s="20" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B50" s="15"/>
     </row>
-    <row r="51" spans="1:2" customFormat="1">
-      <c r="A51" s="16" t="s">
-        <v>47</v>
+    <row r="51" spans="1:2">
+      <c r="A51" s="20" t="s">
+        <v>60</v>
       </c>
       <c r="B51" s="15"/>
     </row>
-    <row r="52" spans="1:2" customFormat="1">
-      <c r="A52" s="14" t="s">
-        <v>48</v>
+    <row r="52" spans="1:2">
+      <c r="A52" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="B52" s="15"/>
     </row>
-    <row r="53" spans="1:2" customFormat="1">
-      <c r="A53" s="16"/>
+    <row r="53" spans="1:2">
+      <c r="A53" s="14" t="s">
+        <v>62</v>
+      </c>
       <c r="B53" s="15"/>
     </row>
     <row r="54" spans="1:2">
@@ -1087,12 +1215,12 @@
       <c r="B54" s="15"/>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="17"/>
-      <c r="B55" s="12"/>
+      <c r="A55" s="16"/>
+      <c r="B55" s="15"/>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="17"/>
-      <c r="B56" s="18"/>
+      <c r="B56" s="12"/>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="17"/>
@@ -1112,16 +1240,17 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="17"/>
-      <c r="B61" s="12"/>
+      <c r="B61" s="18"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="17"/>
       <c r="B62" s="12"/>
     </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="17"/>
+      <c r="B63" s="12"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B8">
-    <sortCondition ref="A2"/>
-  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1140,37 +1269,37 @@
     <col min="7" max="7" width="17.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="22.8">
-      <c r="A1" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+    <row r="1" spans="1:8" ht="22.8" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="2" spans="1:8" s="4" customFormat="1" ht="30" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H2" s="6"/>
     </row>
@@ -1181,54 +1310,54 @@
       <c r="D3" s="24"/>
       <c r="E3" s="24"/>
       <c r="F3" s="24"/>
-      <c r="G3" s="25"/>
+      <c r="G3" s="27"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="25"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="24"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
       <c r="G5" s="25"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
       <c r="G6" s="25"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="25"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="F3:F7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D3:D7"/>
     <mergeCell ref="G3:G7"/>
-    <mergeCell ref="E3:E7"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C3:C7"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="B3:B7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="E3:E7"/>
+    <mergeCell ref="F3:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1250,60 +1379,60 @@
     <col min="13" max="13" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="22.8">
+    <row r="1" spans="1:13" ht="22.8" customHeight="1">
       <c r="C1" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="19.95" customHeight="1"/>
@@ -1323,17 +1452,216 @@
   <mergeCells count="1">
     <mergeCell ref="C1:M1"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K15" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"Conversation/Short Sentences,Synonym,Antonym,Pronunciation,Grammar,Sentence Meaning,Sentence Combining,Fill in Blank,Reading Comprehension,Arrangement"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L21" xr:uid="{00000000-0002-0000-0200-000001000000}">
-      <formula1>"Easy,Medium,Hard,Very Hard"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M21" xr:uid="{00000000-0002-0000-0200-000002000000}">
-      <formula1>"Notice Completion,Flyer Completion,Passage Arrangement,Information Gap Filling,Reading Comprehension"</formula1>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Correct Answer" error="Please select a valid Correct Answer: A, B, C, or D." promptTitle="Correct Answer" prompt="Choose the Correct Answer (A, B, C, or D)." sqref="I3:I21" xr:uid="{00000000-0002-0000-0200-000003000000}">
+      <formula1>"A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid Skill Type" error="Please select a valid Skill Type from the list." promptTitle="Skill Type" prompt="Choose a Skill Type from the dropdown." xr:uid="{00000000-0002-0000-0200-000000000000}">
+          <x14:formula1>
+            <xm:f>LISTS_DATA!$A$2:$A$27</xm:f>
+          </x14:formula1>
+          <xm:sqref>K3:K21</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid Difficulty" error="Please select a valid Difficulty from the list." promptTitle="Difficulty" prompt="Choose a Difficulty from the dropdown." xr:uid="{00000000-0002-0000-0200-000001000000}">
+          <x14:formula1>
+            <xm:f>LISTS_DATA!$B$2:$B$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>L3:L21</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid Group Type" error="Please select a valid Group Type from the list." promptTitle="Group Type" prompt="Choose a Group Type from the dropdown." xr:uid="{00000000-0002-0000-0200-000002000000}">
+          <x14:formula1>
+            <xm:f>LISTS_DATA!$C$2:$C$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>M3:M21</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/doc/templates/Hango_Exam_Import_Template.xlsx
+++ b/doc/templates/Hango_Exam_Import_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Summer2026\SEP490\project\HanGo\doc\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25D54CD-12B9-4611-A6E4-6E5BB2F85BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3F9BF7-16E4-42AE-93C6-039E9DDB10F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="108">
   <si>
     <t>QUESTIONS</t>
   </si>
@@ -109,9 +109,6 @@
     <t xml:space="preserve">   - Skill Type must exactly match one of the following names:</t>
   </si>
   <si>
-    <t xml:space="preserve">      + Phonetics</t>
-  </si>
-  <si>
     <t xml:space="preserve">      + Word order</t>
   </si>
   <si>
@@ -344,6 +341,12 @@
   </si>
   <si>
     <t>Sentence insertion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      + Part of speech / Participle</t>
+  </si>
+  <si>
+    <t>Part of speech / Participle</t>
   </si>
 </sst>
 </file>
@@ -573,19 +576,19 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -996,217 +999,217 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="20" t="s">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="B18" s="15"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" s="15"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="15"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" s="15"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22" s="15"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="15"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="15"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="15"/>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" s="15"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B27" s="15"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="15"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="15"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="15"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="15"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32" s="15"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B33" s="15"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B34" s="15"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" s="15"/>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B36" s="15"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" s="15"/>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B38" s="15"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B39" s="15"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B40" s="15"/>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B41" s="15"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B42" s="15"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B43" s="15"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B44" s="15"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B45" s="15"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B46" s="15"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B47" s="15"/>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B48" s="15"/>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B49" s="15"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B50" s="15"/>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B51" s="15"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B52" s="15"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B53" s="15"/>
     </row>
@@ -1270,8 +1273,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.8" customHeight="1">
-      <c r="A1" s="23" t="s">
-        <v>63</v>
+      <c r="A1" s="21" t="s">
+        <v>62</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -1284,69 +1287,69 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="24"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="27"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="26"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="25"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="26"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1380,7 +1383,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="22.8" customHeight="1">
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="27" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="22"/>
@@ -1463,7 +1466,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid Skill Type" error="Please select a valid Skill Type from the list." promptTitle="Skill Type" prompt="Choose a Skill Type from the dropdown." xr:uid="{00000000-0002-0000-0200-000000000000}">
           <x14:formula1>
-            <xm:f>LISTS_DATA!$A$2:$A$27</xm:f>
+            <xm:f>LISTS_DATA!$A$2:$A$28</xm:f>
           </x14:formula1>
           <xm:sqref>K3:K21</xm:sqref>
         </x14:dataValidation>
@@ -1487,7 +1490,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1503,162 +1506,167 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" t="s">
         <v>70</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
         <v>73</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>74</v>
-      </c>
-      <c r="C3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" t="s">
         <v>76</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" t="s">
         <v>79</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>80</v>
-      </c>
-      <c r="C5" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" t="s">
         <v>82</v>
-      </c>
-      <c r="C6" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
         <v>84</v>
-      </c>
-      <c r="C7" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>106</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
